--- a/BharatFinTrack/base_data/base_equity_index.xlsx
+++ b/BharatFinTrack/base_data/base_equity_index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Debasish\Documents\coding\pypi_own\pypi_BharatFinTrack\BharatFinTrack\base_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AABF882-ED42-41BA-9CA4-1E0367142D1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF47F09-CA66-42B0-A1C6-AC0B3243338C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="broad" sheetId="7" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="194">
   <si>
     <t>NIFTY 50</t>
   </si>
@@ -616,6 +616,9 @@
   </si>
   <si>
     <t>NIFTY500 GROWTH 50</t>
+  </si>
+  <si>
+    <t>NIFTY AI CATALYSTS</t>
   </si>
 </sst>
 </file>
@@ -1892,7 +1895,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{466D5EDC-7427-4A89-B90E-E56187B74B61}">
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="55.6640625" style="1" customWidth="1"/>
@@ -2612,6 +2615,20 @@
       </c>
       <c r="D51" t="s">
         <v>160</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B52" s="3">
+        <v>45471</v>
+      </c>
+      <c r="C52">
+        <v>1000</v>
+      </c>
+      <c r="D52" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>

--- a/BharatFinTrack/base_data/base_equity_index.xlsx
+++ b/BharatFinTrack/base_data/base_equity_index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Debasish\Documents\coding\pypi_own\pypi_BharatFinTrack\BharatFinTrack\base_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF47F09-CA66-42B0-A1C6-AC0B3243338C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A25957E2-D0AC-4E00-8024-E4B27B9550BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="broad" sheetId="7" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="195">
   <si>
     <t>NIFTY 50</t>
   </si>
@@ -619,6 +619,9 @@
   </si>
   <si>
     <t>NIFTY AI CATALYSTS</t>
+  </si>
+  <si>
+    <t>NIFTY HIGH DIVIDEND YIELD 15</t>
   </si>
 </sst>
 </file>
@@ -628,7 +631,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-14009]dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -646,6 +649,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -686,7 +696,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -705,6 +715,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2643,7 +2654,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{898D7280-DA99-43BB-B8CC-2B757AFDF5E9}">
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.6640625" style="1" customWidth="1"/>
@@ -2820,8 +2831,8 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>61</v>
+      <c r="A13" s="8" t="s">
+        <v>194</v>
       </c>
       <c r="B13" s="4">
         <v>38443</v>
@@ -2829,13 +2840,13 @@
       <c r="C13">
         <v>1000</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>61</v>
+      <c r="D13" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B14" s="4">
         <v>38443</v>
@@ -2844,12 +2855,12 @@
         <v>1000</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>131</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="B15" s="4">
         <v>38443</v>
@@ -2858,12 +2869,12 @@
         <v>1000</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>90</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="B16" s="4">
         <v>38443</v>
@@ -2872,12 +2883,12 @@
         <v>1000</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>50</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="B17" s="4">
         <v>38443</v>
@@ -2886,12 +2897,12 @@
         <v>1000</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B18" s="4">
         <v>38443</v>
@@ -2900,12 +2911,12 @@
         <v>1000</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>155</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>167</v>
+        <v>62</v>
       </c>
       <c r="B19" s="4">
         <v>38443</v>
@@ -2914,12 +2925,12 @@
         <v>1000</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>56</v>
+        <v>167</v>
       </c>
       <c r="B20" s="4">
         <v>38443</v>
@@ -2928,82 +2939,82 @@
         <v>1000</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>56</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="4">
+        <v>38443</v>
+      </c>
+      <c r="C21">
+        <v>1000</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="4">
-        <v>38443</v>
-      </c>
-      <c r="C21">
-        <v>1000</v>
-      </c>
-      <c r="D21" s="1" t="s">
+      <c r="B22" s="4">
+        <v>38443</v>
+      </c>
+      <c r="C22">
+        <v>1000</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B22" s="4">
-        <v>38443</v>
-      </c>
-      <c r="C22">
-        <v>1000</v>
-      </c>
-      <c r="D22" s="5" t="s">
+      <c r="B23" s="4">
+        <v>38443</v>
+      </c>
+      <c r="C23">
+        <v>1000</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B23" s="4">
-        <v>38443</v>
-      </c>
-      <c r="C23">
-        <v>1000</v>
-      </c>
-      <c r="D23" s="1" t="s">
+      <c r="B24" s="4">
+        <v>38443</v>
+      </c>
+      <c r="C24">
+        <v>1000</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="4">
-        <v>38443</v>
-      </c>
-      <c r="C24">
-        <v>1000</v>
-      </c>
-      <c r="D24" s="5" t="s">
+      <c r="B25" s="4">
+        <v>38443</v>
+      </c>
+      <c r="C25">
+        <v>1000</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>51</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B25" s="4">
-        <v>38443</v>
-      </c>
-      <c r="C25">
-        <v>1000</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B26" s="4">
         <v>38443</v>
@@ -3012,12 +3023,12 @@
         <v>1000</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>192</v>
+        <v>99</v>
       </c>
       <c r="B27" s="4">
         <v>38443</v>
@@ -3025,13 +3036,13 @@
       <c r="C27">
         <v>1000</v>
       </c>
-      <c r="D27" t="s">
-        <v>192</v>
+      <c r="D27" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="B28" s="4">
         <v>38443</v>
@@ -3040,54 +3051,54 @@
         <v>1000</v>
       </c>
       <c r="D28" t="s">
-        <v>159</v>
+        <v>192</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B29" s="4">
+        <v>38443</v>
+      </c>
+      <c r="C29">
+        <v>1000</v>
+      </c>
+      <c r="D29" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B29" s="4">
-        <v>38443</v>
-      </c>
-      <c r="C29">
-        <v>1000</v>
-      </c>
-      <c r="D29" s="1" t="s">
+      <c r="B30" s="4">
+        <v>38443</v>
+      </c>
+      <c r="C30">
+        <v>1000</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="5" t="s">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B30" s="4">
-        <v>38443</v>
-      </c>
-      <c r="C30">
-        <v>1000</v>
-      </c>
-      <c r="D30" s="5" t="s">
+      <c r="B31" s="4">
+        <v>38443</v>
+      </c>
+      <c r="C31">
+        <v>1000</v>
+      </c>
+      <c r="D31" s="5" t="s">
         <v>106</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="B31" s="4">
-        <v>38443</v>
-      </c>
-      <c r="C31">
-        <v>1000</v>
-      </c>
-      <c r="D31" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B32" s="4">
         <v>38443</v>
@@ -3096,12 +3107,12 @@
         <v>1000</v>
       </c>
       <c r="D32" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>57</v>
+        <v>156</v>
       </c>
       <c r="B33" s="4">
         <v>38443</v>
@@ -3109,27 +3120,27 @@
       <c r="C33">
         <v>1000</v>
       </c>
-      <c r="D33" s="1" t="s">
-        <v>57</v>
+      <c r="D33" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B34" s="4">
+        <v>38443</v>
+      </c>
+      <c r="C34">
+        <v>1000</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="B34" s="4">
-        <v>38778</v>
-      </c>
-      <c r="C34">
-        <v>1000</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="7" t="s">
-        <v>150</v>
       </c>
       <c r="B35" s="4">
         <v>38778</v>
@@ -3137,13 +3148,13 @@
       <c r="C35">
         <v>1000</v>
       </c>
-      <c r="D35" s="7" t="s">
-        <v>150</v>
+      <c r="D35" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B36" s="4">
         <v>38778</v>
@@ -3152,40 +3163,40 @@
         <v>1000</v>
       </c>
       <c r="D36" s="7" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="7" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="B37" s="4">
-        <v>39356</v>
+        <v>38778</v>
       </c>
       <c r="C37">
         <v>1000</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>117</v>
+      <c r="D37" s="7" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B38" s="4">
-        <v>39814</v>
+        <v>39356</v>
       </c>
       <c r="C38">
         <v>1000</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B39" s="4">
         <v>39814</v>
@@ -3194,26 +3205,26 @@
         <v>1000</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>55</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B40" s="3">
-        <v>39905</v>
+        <v>55</v>
+      </c>
+      <c r="B40" s="4">
+        <v>39814</v>
       </c>
       <c r="C40">
         <v>1000</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>147</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B41" s="3">
         <v>39905</v>
@@ -3227,7 +3238,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B42" s="3">
         <v>39905</v>
@@ -3241,7 +3252,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B43" s="3">
         <v>39905</v>
@@ -3255,21 +3266,21 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B44" s="4">
-        <v>40087</v>
+        <v>88</v>
+      </c>
+      <c r="B44" s="3">
+        <v>39905</v>
       </c>
       <c r="C44">
         <v>1000</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>163</v>
+        <v>49</v>
       </c>
       <c r="B45" s="4">
         <v>40087</v>
@@ -3277,28 +3288,42 @@
       <c r="C45">
         <v>1000</v>
       </c>
-      <c r="D45" t="s">
-        <v>163</v>
+      <c r="D45" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B46" s="4">
+        <v>40087</v>
+      </c>
+      <c r="C46">
+        <v>1000</v>
+      </c>
+      <c r="D46" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B46" s="3">
+      <c r="B47" s="3">
         <v>40269</v>
       </c>
-      <c r="C46">
-        <v>1000</v>
-      </c>
-      <c r="D46" s="1" t="s">
+      <c r="C47">
+        <v>1000</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>147</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D46">
-    <sortCondition ref="B2:B46"/>
-    <sortCondition ref="A2:A46"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D47">
+    <sortCondition ref="B2:B47"/>
+    <sortCondition ref="A2:A47"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
